--- a/Documentation/Week 6/Booked Hours/Booked_Hours_Terry.xlsx
+++ b/Documentation/Week 6/Booked Hours/Booked_Hours_Terry.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CITS3200\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 6/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2C53A194341BF849221DADA6222B49715C8BDCBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73371DB7-2FD4-43D4-9F30-BB70F7AE4C92}"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -130,15 +131,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -157,357 +154,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Lucida Sans"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -655,291 +315,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -950,15 +332,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -974,62 +348,59 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
@@ -1102,6 +473,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1423,137 +797,137 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="5.8359375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3359375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3359375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.8359375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3359375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="1"/>
-    <col min="9" max="9" width="10.6640625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6640625" style="1"/>
+    <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="46.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="71" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.05" customHeight="1">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="13" customHeight="1" spans="1:9">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="s">
+    <row r="3" spans="1:9" ht="13.05" customHeight="1">
+      <c r="A3" s="14"/>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="14"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="4">
         <v>44770</v>
       </c>
-      <c r="C4" s="16">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D4" s="17">
+      <c r="C4" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="6">
         <v>44770</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="5">
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="7">
         <f>IF(I4&gt;0,I4,IF(I4=0," ","ERROR"))</f>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
       <c r="H4" s="1">
         <f>IF(G4&lt;&gt;"ERROR",G4)</f>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
       <c r="I4" s="1">
         <f>((D4+E4)-(B4+C4))*24</f>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="4">
         <v>44771</v>
       </c>
-      <c r="C5" s="16">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D5" s="17">
+      <c r="C5" s="5">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D5" s="6">
         <v>44771</v>
       </c>
-      <c r="E5" s="16">
-        <v>0.645833333333333</v>
+      <c r="E5" s="5">
+        <v>0.64583333333333304</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="7">
         <f t="shared" ref="G5:G30" si="0">IF(I5&gt;0,I5,IF(I5=0," ","ERROR"))</f>
         <v>1.5</v>
       </c>
       <c r="H5" s="1">
         <f>IF(AND(G5&lt;&gt;" ",G5&lt;&gt;"ERROR",H4&lt;&gt;" ",H4&lt;&gt;"ERROR"),G5+H4," ")</f>
-        <v>2.49999999994179</v>
+        <v>2.4999999999417901</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I68" si="1">((D5+E5)-(B5+C5))*24</f>
@@ -1564,28 +938,28 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="4">
         <v>44772</v>
       </c>
-      <c r="C6" s="16">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="C6" s="5">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="D6" s="6">
         <v>44772</v>
       </c>
-      <c r="E6" s="16">
-        <v>0.666666666666667</v>
+      <c r="E6" s="5">
+        <v>0.66666666666666696</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="7">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" ref="H6:H30" si="2">IF(AND(G6&lt;&gt;" ",G6&lt;&gt;"ERROR",H5&lt;&gt;" ",H5&lt;&gt;"ERROR"),G6+H5," ")</f>
-        <v>3.99999999994179</v>
+        <v>3.9999999999417901</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
@@ -1596,88 +970,88 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="4">
         <v>44777</v>
       </c>
-      <c r="C7" s="16">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="C7" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D7" s="6">
         <v>44777</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="5">
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
       <c r="H7" s="1">
         <f t="shared" si="2"/>
-        <v>4.99999999988358</v>
+        <v>4.9999999998835802</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>3</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="4">
         <v>44778</v>
       </c>
-      <c r="C8" s="16">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="D8" s="17">
+      <c r="C8" s="5">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D8" s="6">
         <v>44778</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="5">
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v>2.00000000005821</v>
+        <v>2.0000000000582099</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="2"/>
-        <v>6.99999999994179</v>
+        <v>6.9999999999417897</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="1"/>
-        <v>2.00000000005821</v>
+        <v>2.0000000000582099</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>3</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="4">
         <v>44779</v>
       </c>
-      <c r="C9" s="16">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D9" s="17">
+      <c r="C9" s="5">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D9" s="6">
         <v>44779</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="5">
         <v>0.625</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>2.00000000005821</v>
+        <v>2.0000000000582099</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="2"/>
@@ -1685,99 +1059,99 @@
       </c>
       <c r="I9" s="1">
         <f t="shared" si="1"/>
-        <v>2.00000000005821</v>
+        <v>2.0000000000582099</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>4</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="6">
         <v>44784</v>
       </c>
-      <c r="C10" s="16">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D10" s="17">
+      <c r="C10" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D10" s="6">
         <v>44784</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="5">
         <v>0.5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="2"/>
-        <v>9.99999999994179</v>
+        <v>9.9999999999417906</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="6">
         <v>44784</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="5">
         <v>0.625</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="6">
         <v>44784</v>
       </c>
-      <c r="E11" s="16">
-        <v>0.666666666666667</v>
+      <c r="E11" s="5">
+        <v>0.66666666666666696</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="2"/>
-        <v>10.9999999998836</v>
+        <v>10.999999999883601</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="6">
         <v>44787</v>
       </c>
-      <c r="C12" s="16">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="C12" s="5">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D12" s="6">
         <v>44787</v>
       </c>
-      <c r="E12" s="16">
-        <v>0.479166666666667</v>
+      <c r="E12" s="5">
+        <v>0.47916666666666702</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="7">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="2"/>
-        <v>12.4999999998836</v>
+        <v>12.499999999883601</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="1"/>
@@ -1788,22 +1162,22 @@
       <c r="A13" s="1">
         <v>4</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="6">
         <v>44788</v>
       </c>
-      <c r="C13" s="16">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="D13" s="17">
+      <c r="C13" s="5">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="D13" s="6">
         <v>44788</v>
       </c>
-      <c r="E13" s="16">
-        <v>0.708333333333333</v>
+      <c r="E13" s="5">
+        <v>0.70833333333333304</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="7">
         <f t="shared" si="0"/>
         <v>1.00000000011642</v>
       </c>
@@ -1820,28 +1194,28 @@
       <c r="A14" s="1">
         <v>5</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="6">
         <v>44790</v>
       </c>
-      <c r="C14" s="16">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D14" s="17">
+      <c r="C14" s="5">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D14" s="6">
         <v>44790</v>
       </c>
-      <c r="E14" s="16">
-        <v>0.666666666666667</v>
+      <c r="E14" s="5">
+        <v>0.66666666666666696</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="7">
         <f t="shared" si="0"/>
         <v>1.99999999988358</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="2"/>
-        <v>15.4999999998836</v>
+        <v>15.499999999883601</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="1"/>
@@ -1852,206 +1226,206 @@
       <c r="A15" s="1">
         <v>5</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="6">
         <v>44791</v>
       </c>
-      <c r="C15" s="16">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D15" s="17">
+      <c r="C15" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="6">
         <v>44791</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="5">
         <v>0.5</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="2"/>
-        <v>16.4999999998254</v>
+        <v>16.499999999825398</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.99999999994179201</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>5</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="6">
         <v>44792</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="5">
         <v>0.875</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="6">
         <v>44792</v>
       </c>
-      <c r="E16" s="16">
-        <v>0.958333333333333</v>
+      <c r="E16" s="5">
+        <v>0.95833333333333304</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="7">
         <f t="shared" si="0"/>
-        <v>2.00000000005821</v>
+        <v>2.0000000000582099</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="2"/>
-        <v>18.4999999998836</v>
+        <v>18.499999999883599</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
-        <v>2.00000000005821</v>
+        <v>2.0000000000582099</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>5</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="6">
         <v>44791</v>
       </c>
-      <c r="C17" s="16">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D17" s="17">
+      <c r="C17" s="5">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D17" s="6">
         <v>44791</v>
       </c>
-      <c r="E17" s="16">
-        <v>0.569444444444444</v>
+      <c r="E17" s="5">
+        <v>0.56944444444444398</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="7">
         <f t="shared" si="0"/>
-        <v>0.666666666744277</v>
+        <v>0.66666666674427699</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>19.1666666666279</v>
+        <v>19.166666666627901</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
-        <v>0.666666666744277</v>
+        <v>0.66666666674427699</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>6</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="6">
         <v>44798</v>
       </c>
-      <c r="C18" s="16">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D18" s="17">
+      <c r="C18" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="6">
         <v>44798</v>
       </c>
-      <c r="E18" s="16">
-        <v>0.5</v>
+      <c r="E18" s="5">
+        <v>0.48958333333333331</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.75</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v>20.1666666665697</v>
+        <v>19.916666666627901</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>6</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="6">
         <v>44798</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="5">
         <v>0.5</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="6">
         <v>44798</v>
       </c>
-      <c r="E19" s="16">
-        <v>0.541666666666667</v>
+      <c r="E19" s="5">
+        <v>0.53125</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.75</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="2"/>
-        <v>21.1666666665114</v>
+        <v>20.666666666627901</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>6</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="6">
         <v>44800</v>
       </c>
-      <c r="C20" s="16">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="D20" s="17">
+      <c r="C20" s="5">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="D20" s="6">
         <v>44800</v>
       </c>
-      <c r="E20" s="16">
-        <v>0.6875</v>
+      <c r="E20" s="5">
+        <v>0.66666666666666663</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="7">
         <f t="shared" si="0"/>
-        <v>0.999999999941792</v>
+        <v>0.49999999988358468</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="2"/>
-        <v>22.1666666664532</v>
+        <v>21.166666666511485</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>0.999999999941792</v>
+        <v>0.49999999988358468</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="B21" s="17"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="16"/>
-      <c r="G21" s="18" t="str">
+      <c r="B21" s="6"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="5"/>
+      <c r="G21" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H21" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
@@ -2059,17 +1433,17 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="B22" s="17"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="16"/>
-      <c r="G22" s="18" t="str">
+      <c r="B22" s="6"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
+      <c r="G22" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H22" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H22" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
@@ -2077,17 +1451,17 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="B23" s="17"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="16"/>
-      <c r="G23" s="18" t="str">
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="5"/>
+      <c r="G23" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H23" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H23" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="1"/>
@@ -2095,17 +1469,17 @@
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="B24" s="17"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="16"/>
-      <c r="G24" s="18" t="str">
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="5"/>
+      <c r="G24" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H24" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H24" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="1"/>
@@ -2113,17 +1487,17 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="B25" s="17"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="16"/>
-      <c r="G25" s="18" t="str">
+      <c r="B25" s="6"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="5"/>
+      <c r="G25" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H25" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H25" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="1"/>
@@ -2131,17 +1505,17 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="B26" s="17"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="16"/>
-      <c r="G26" s="18" t="str">
+      <c r="B26" s="6"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="5"/>
+      <c r="G26" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H26" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H26" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="1"/>
@@ -2149,17 +1523,17 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="B27" s="17"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="16"/>
-      <c r="G27" s="18" t="str">
+      <c r="B27" s="6"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="5"/>
+      <c r="G27" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H27" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="1"/>
@@ -2167,17 +1541,17 @@
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="B28" s="17"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="16"/>
-      <c r="G28" s="18" t="str">
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="5"/>
+      <c r="G28" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H28" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="1"/>
@@ -2185,17 +1559,17 @@
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="B29" s="17"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="16"/>
-      <c r="G29" s="18" t="str">
+      <c r="B29" s="6"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H29" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H29" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="1"/>
@@ -2203,42 +1577,42 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="B30" s="17"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="16"/>
-      <c r="G30" s="18" t="str">
+      <c r="B30" s="6"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="5"/>
+      <c r="G30" s="7" t="str">
         <f t="shared" si="0"/>
-        <v> </v>
-      </c>
-      <c r="H30" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H30" s="1" t="e">
         <f t="shared" si="2"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="15" spans="1:9">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:9" ht="15">
+      <c r="A31" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="12"/>
+      <c r="D31" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="19" t="s">
+      <c r="E31" s="12"/>
+      <c r="F31" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="17" t="s">
         <v>6</v>
       </c>
       <c r="I31" s="1" t="e">
@@ -2246,40 +1620,40 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="1:9">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11" t="s">
+    <row r="32" spans="1:9" ht="15">
+      <c r="A32" s="14"/>
+      <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
       <c r="I32" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="17"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="G33" s="18" t="str">
+      <c r="B33" s="6"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="5"/>
+      <c r="G33" s="7" t="str">
         <f t="shared" ref="G33:G64" si="3">IF(I33&gt;0,I33,IF(I33=0," ","ERROR"))</f>
-        <v> </v>
-      </c>
-      <c r="H33" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H33" s="1" t="e">
         <f>IF(AND(G33&lt;&gt;" ",G33&lt;&gt;"ERROR",H30&lt;&gt;" ",H30&lt;&gt;"ERROR"),G33+H30," ")</f>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="1"/>
@@ -2287,17 +1661,17 @@
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="17"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="16"/>
-      <c r="G34" s="18" t="str">
+      <c r="B34" s="6"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="5"/>
+      <c r="G34" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H34" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="1" t="e">
         <f t="shared" ref="H34:H64" si="4">IF(AND(G34&lt;&gt;" ",G34&lt;&gt;"ERROR",H33&lt;&gt;" ",H33&lt;&gt;"ERROR"),G34+H33," ")</f>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="1"/>
@@ -2305,17 +1679,17 @@
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="17"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="16"/>
-      <c r="G35" s="18" t="str">
+      <c r="B35" s="6"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="5"/>
+      <c r="G35" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H35" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="1"/>
@@ -2323,17 +1697,17 @@
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="17"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="16"/>
-      <c r="G36" s="18" t="str">
+      <c r="B36" s="6"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="5"/>
+      <c r="G36" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H36" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H36" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="1"/>
@@ -2341,17 +1715,17 @@
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="17"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="16"/>
-      <c r="G37" s="18" t="str">
+      <c r="B37" s="6"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="5"/>
+      <c r="G37" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H37" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H37" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="1"/>
@@ -2359,17 +1733,17 @@
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="17"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="16"/>
-      <c r="G38" s="18" t="str">
+      <c r="B38" s="6"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="5"/>
+      <c r="G38" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H38" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H38" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="1"/>
@@ -2377,17 +1751,17 @@
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="17"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="16"/>
-      <c r="G39" s="18" t="str">
+      <c r="B39" s="6"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="5"/>
+      <c r="G39" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H39" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="1"/>
@@ -2395,17 +1769,17 @@
       </c>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="17"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="16"/>
-      <c r="G40" s="18" t="str">
+      <c r="B40" s="6"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="5"/>
+      <c r="G40" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H40" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="1"/>
@@ -2413,17 +1787,17 @@
       </c>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="17"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="16"/>
-      <c r="G41" s="18" t="str">
+      <c r="B41" s="6"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="5"/>
+      <c r="G41" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H41" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="1"/>
@@ -2431,17 +1805,17 @@
       </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="17"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="16"/>
-      <c r="G42" s="18" t="str">
+      <c r="B42" s="6"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="5"/>
+      <c r="G42" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H42" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="1"/>
@@ -2449,17 +1823,17 @@
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="17"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="16"/>
-      <c r="G43" s="18" t="str">
+      <c r="B43" s="6"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="5"/>
+      <c r="G43" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H43" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H43" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="1"/>
@@ -2467,17 +1841,17 @@
       </c>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="17"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="16"/>
-      <c r="G44" s="18" t="str">
+      <c r="B44" s="6"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="5"/>
+      <c r="G44" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H44" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H44" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="1"/>
@@ -2485,17 +1859,17 @@
       </c>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="17"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="16"/>
-      <c r="G45" s="18" t="str">
+      <c r="B45" s="6"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="5"/>
+      <c r="G45" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H45" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H45" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="1"/>
@@ -2503,17 +1877,17 @@
       </c>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="17"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="16"/>
-      <c r="G46" s="18" t="str">
+      <c r="B46" s="6"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="5"/>
+      <c r="G46" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H46" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H46" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I46" s="1">
         <f t="shared" si="1"/>
@@ -2521,17 +1895,17 @@
       </c>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="17"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="16"/>
-      <c r="G47" s="18" t="str">
+      <c r="B47" s="6"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="5"/>
+      <c r="G47" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H47" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H47" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I47" s="1">
         <f t="shared" si="1"/>
@@ -2539,17 +1913,17 @@
       </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="17"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="16"/>
-      <c r="G48" s="18" t="str">
+      <c r="B48" s="6"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="5"/>
+      <c r="G48" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H48" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H48" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="1"/>
@@ -2557,17 +1931,17 @@
       </c>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="17"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="16"/>
-      <c r="G49" s="18" t="str">
+      <c r="B49" s="6"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="5"/>
+      <c r="G49" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H49" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H49" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="1"/>
@@ -2575,17 +1949,17 @@
       </c>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="17"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="16"/>
-      <c r="G50" s="18" t="str">
+      <c r="B50" s="6"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="5"/>
+      <c r="G50" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H50" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H50" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="1"/>
@@ -2593,17 +1967,17 @@
       </c>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="17"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="16"/>
-      <c r="G51" s="18" t="str">
+      <c r="B51" s="6"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="5"/>
+      <c r="G51" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H51" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H51" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="1"/>
@@ -2611,17 +1985,17 @@
       </c>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="17"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="16"/>
-      <c r="G52" s="18" t="str">
+      <c r="B52" s="6"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="5"/>
+      <c r="G52" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H52" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="1"/>
@@ -2629,17 +2003,17 @@
       </c>
     </row>
     <row r="53" spans="2:9">
-      <c r="B53" s="17"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="16"/>
-      <c r="G53" s="18" t="str">
+      <c r="B53" s="6"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="5"/>
+      <c r="G53" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H53" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="1"/>
@@ -2647,17 +2021,17 @@
       </c>
     </row>
     <row r="54" spans="2:9">
-      <c r="B54" s="17"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="16"/>
-      <c r="G54" s="18" t="str">
+      <c r="B54" s="6"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="5"/>
+      <c r="G54" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H54" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H54" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="1"/>
@@ -2665,17 +2039,17 @@
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="B55" s="17"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="16"/>
-      <c r="G55" s="18" t="str">
+      <c r="B55" s="6"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="5"/>
+      <c r="G55" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H55" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H55" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="1"/>
@@ -2683,17 +2057,17 @@
       </c>
     </row>
     <row r="56" spans="2:9">
-      <c r="B56" s="17"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="16"/>
-      <c r="G56" s="18" t="str">
+      <c r="B56" s="6"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="5"/>
+      <c r="G56" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H56" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H56" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I56" s="1">
         <f t="shared" si="1"/>
@@ -2701,17 +2075,17 @@
       </c>
     </row>
     <row r="57" spans="2:9">
-      <c r="B57" s="17"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="16"/>
-      <c r="G57" s="18" t="str">
+      <c r="B57" s="6"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="5"/>
+      <c r="G57" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H57" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H57" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I57" s="1">
         <f t="shared" si="1"/>
@@ -2719,17 +2093,17 @@
       </c>
     </row>
     <row r="58" spans="2:9">
-      <c r="B58" s="17"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="16"/>
-      <c r="G58" s="18" t="str">
+      <c r="B58" s="6"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="5"/>
+      <c r="G58" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H58" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H58" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I58" s="1">
         <f t="shared" si="1"/>
@@ -2737,17 +2111,17 @@
       </c>
     </row>
     <row r="59" spans="2:9">
-      <c r="B59" s="17"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="16"/>
-      <c r="G59" s="18" t="str">
+      <c r="B59" s="6"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="5"/>
+      <c r="G59" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H59" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I59" s="1">
         <f t="shared" si="1"/>
@@ -2755,14 +2129,14 @@
       </c>
     </row>
     <row r="60" spans="2:9">
-      <c r="B60" s="17"/>
-      <c r="G60" s="18" t="str">
+      <c r="B60" s="6"/>
+      <c r="G60" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H60" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H60" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I60" s="1">
         <f t="shared" si="1"/>
@@ -2770,14 +2144,14 @@
       </c>
     </row>
     <row r="61" spans="2:9">
-      <c r="B61" s="17"/>
-      <c r="G61" s="18" t="str">
+      <c r="B61" s="6"/>
+      <c r="G61" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H61" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I61" s="1">
         <f t="shared" si="1"/>
@@ -2785,14 +2159,14 @@
       </c>
     </row>
     <row r="62" spans="2:9">
-      <c r="B62" s="17"/>
-      <c r="G62" s="18" t="str">
+      <c r="B62" s="6"/>
+      <c r="G62" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H62" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H62" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I62" s="1">
         <f t="shared" si="1"/>
@@ -2800,14 +2174,14 @@
       </c>
     </row>
     <row r="63" spans="2:9">
-      <c r="B63" s="17"/>
-      <c r="G63" s="18" t="str">
+      <c r="B63" s="6"/>
+      <c r="G63" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H63" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H63" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I63" s="1">
         <f t="shared" si="1"/>
@@ -2815,39 +2189,39 @@
       </c>
     </row>
     <row r="64" spans="2:9">
-      <c r="B64" s="17"/>
-      <c r="G64" s="18" t="str">
+      <c r="B64" s="6"/>
+      <c r="G64" s="7" t="str">
         <f t="shared" si="3"/>
-        <v> </v>
-      </c>
-      <c r="H64" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H64" s="1" t="e">
         <f t="shared" si="4"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I64" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="15" spans="1:9">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="1:9" ht="15">
+      <c r="A65" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="6" t="s">
+      <c r="C65" s="12"/>
+      <c r="D65" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E65" s="7"/>
-      <c r="F65" s="19" t="s">
+      <c r="E65" s="12"/>
+      <c r="F65" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G65" s="19" t="s">
+      <c r="G65" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H65" s="19" t="s">
+      <c r="H65" s="17" t="s">
         <v>6</v>
       </c>
       <c r="I65" s="1" t="e">
@@ -2855,36 +2229,36 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" ht="15" spans="1:9">
-      <c r="A66" s="10"/>
-      <c r="B66" s="11" t="s">
+    <row r="66" spans="1:9" ht="15">
+      <c r="A66" s="14"/>
+      <c r="B66" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
       <c r="I66" s="1" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="G67" s="18" t="str">
+      <c r="G67" s="7" t="str">
         <f t="shared" ref="G67:G98" si="5">IF(I67&gt;0,I67,IF(I67=0," ","ERROR"))</f>
-        <v> </v>
-      </c>
-      <c r="H67" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H67" s="1" t="e">
         <f>IF(AND(G67&lt;&gt;" ",G67&lt;&gt;"ERROR",H64&lt;&gt;" ",H64&lt;&gt;"ERROR"),G67+H64," ")</f>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I67" s="1">
         <f t="shared" si="1"/>
@@ -2892,13 +2266,13 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="G68" s="18" t="str">
+      <c r="G68" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H68" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H68" s="1" t="e">
         <f t="shared" ref="H68:H98" si="6">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ",H67&lt;&gt;"ERROR"),G68+H67," ")</f>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I68" s="1">
         <f t="shared" si="1"/>
@@ -2906,13 +2280,13 @@
       </c>
     </row>
     <row r="69" spans="1:9">
-      <c r="G69" s="18" t="str">
+      <c r="G69" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H69" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H69" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I69" s="1">
         <f t="shared" ref="I69:I132" si="7">((D69+E69)-(B69+C69))*24</f>
@@ -2920,13 +2294,13 @@
       </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="G70" s="18" t="str">
+      <c r="G70" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H70" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H70" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="7"/>
@@ -2934,13 +2308,13 @@
       </c>
     </row>
     <row r="71" spans="1:9">
-      <c r="G71" s="18" t="str">
+      <c r="G71" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H71" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H71" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I71" s="1">
         <f t="shared" si="7"/>
@@ -2948,13 +2322,13 @@
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="G72" s="18" t="str">
+      <c r="G72" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H72" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H72" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="7"/>
@@ -2962,13 +2336,13 @@
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="G73" s="18" t="str">
+      <c r="G73" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H73" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H73" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I73" s="1">
         <f t="shared" si="7"/>
@@ -2976,13 +2350,13 @@
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="G74" s="18" t="str">
+      <c r="G74" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H74" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H74" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I74" s="1">
         <f t="shared" si="7"/>
@@ -2990,13 +2364,13 @@
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="G75" s="18" t="str">
+      <c r="G75" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H75" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H75" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I75" s="1">
         <f t="shared" si="7"/>
@@ -3004,13 +2378,13 @@
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="G76" s="18" t="str">
+      <c r="G76" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H76" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H76" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I76" s="1">
         <f t="shared" si="7"/>
@@ -3018,13 +2392,13 @@
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="G77" s="18" t="str">
+      <c r="G77" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H77" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H77" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I77" s="1">
         <f t="shared" si="7"/>
@@ -3032,13 +2406,13 @@
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="G78" s="18" t="str">
+      <c r="G78" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H78" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H78" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I78" s="1">
         <f t="shared" si="7"/>
@@ -3046,13 +2420,13 @@
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="G79" s="18" t="str">
+      <c r="G79" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H79" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H79" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I79" s="1">
         <f t="shared" si="7"/>
@@ -3060,13 +2434,13 @@
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="G80" s="18" t="str">
+      <c r="G80" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H80" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H80" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I80" s="1">
         <f t="shared" si="7"/>
@@ -3074,13 +2448,13 @@
       </c>
     </row>
     <row r="81" spans="7:9">
-      <c r="G81" s="18" t="str">
+      <c r="G81" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H81" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H81" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I81" s="1">
         <f t="shared" si="7"/>
@@ -3088,13 +2462,13 @@
       </c>
     </row>
     <row r="82" spans="7:9">
-      <c r="G82" s="18" t="str">
+      <c r="G82" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H82" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H82" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I82" s="1">
         <f t="shared" si="7"/>
@@ -3102,13 +2476,13 @@
       </c>
     </row>
     <row r="83" spans="7:9">
-      <c r="G83" s="18" t="str">
+      <c r="G83" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H83" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H83" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I83" s="1">
         <f t="shared" si="7"/>
@@ -3116,13 +2490,13 @@
       </c>
     </row>
     <row r="84" spans="7:9">
-      <c r="G84" s="18" t="str">
+      <c r="G84" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H84" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H84" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I84" s="1">
         <f t="shared" si="7"/>
@@ -3130,13 +2504,13 @@
       </c>
     </row>
     <row r="85" spans="7:9">
-      <c r="G85" s="18" t="str">
+      <c r="G85" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H85" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H85" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I85" s="1">
         <f t="shared" si="7"/>
@@ -3144,13 +2518,13 @@
       </c>
     </row>
     <row r="86" spans="7:9">
-      <c r="G86" s="18" t="str">
+      <c r="G86" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H86" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H86" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I86" s="1">
         <f t="shared" si="7"/>
@@ -3158,13 +2532,13 @@
       </c>
     </row>
     <row r="87" spans="7:9">
-      <c r="G87" s="18" t="str">
+      <c r="G87" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H87" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H87" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I87" s="1">
         <f t="shared" si="7"/>
@@ -3172,13 +2546,13 @@
       </c>
     </row>
     <row r="88" spans="7:9">
-      <c r="G88" s="18" t="str">
+      <c r="G88" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H88" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H88" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I88" s="1">
         <f t="shared" si="7"/>
@@ -3186,13 +2560,13 @@
       </c>
     </row>
     <row r="89" spans="7:9">
-      <c r="G89" s="18" t="str">
+      <c r="G89" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H89" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H89" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I89" s="1">
         <f t="shared" si="7"/>
@@ -3200,13 +2574,13 @@
       </c>
     </row>
     <row r="90" spans="7:9">
-      <c r="G90" s="18" t="str">
+      <c r="G90" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H90" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H90" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I90" s="1">
         <f t="shared" si="7"/>
@@ -3214,13 +2588,13 @@
       </c>
     </row>
     <row r="91" spans="7:9">
-      <c r="G91" s="18" t="str">
+      <c r="G91" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H91" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H91" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I91" s="1">
         <f t="shared" si="7"/>
@@ -3228,13 +2602,13 @@
       </c>
     </row>
     <row r="92" spans="7:9">
-      <c r="G92" s="18" t="str">
+      <c r="G92" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H92" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H92" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I92" s="1">
         <f t="shared" si="7"/>
@@ -3242,13 +2616,13 @@
       </c>
     </row>
     <row r="93" spans="7:9">
-      <c r="G93" s="18" t="str">
+      <c r="G93" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H93" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H93" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I93" s="1">
         <f t="shared" si="7"/>
@@ -3256,13 +2630,13 @@
       </c>
     </row>
     <row r="94" spans="7:9">
-      <c r="G94" s="18" t="str">
+      <c r="G94" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H94" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H94" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I94" s="1">
         <f t="shared" si="7"/>
@@ -3270,13 +2644,13 @@
       </c>
     </row>
     <row r="95" spans="7:9">
-      <c r="G95" s="18" t="str">
+      <c r="G95" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H95" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H95" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I95" s="1">
         <f t="shared" si="7"/>
@@ -3284,13 +2658,13 @@
       </c>
     </row>
     <row r="96" spans="7:9">
-      <c r="G96" s="18" t="str">
+      <c r="G96" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H96" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H96" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I96" s="1">
         <f t="shared" si="7"/>
@@ -3298,13 +2672,13 @@
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="G97" s="18" t="str">
+      <c r="G97" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H97" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H97" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I97" s="1">
         <f t="shared" si="7"/>
@@ -3312,38 +2686,38 @@
       </c>
     </row>
     <row r="98" spans="1:9">
-      <c r="G98" s="18" t="str">
+      <c r="G98" s="7" t="str">
         <f t="shared" si="5"/>
-        <v> </v>
-      </c>
-      <c r="H98" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H98" s="1" t="e">
         <f t="shared" si="6"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I98" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" ht="15" spans="1:9">
-      <c r="A99" s="5" t="s">
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="6" t="s">
+      <c r="C99" s="12"/>
+      <c r="D99" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="19" t="s">
+      <c r="E99" s="12"/>
+      <c r="F99" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G99" s="19" t="s">
+      <c r="G99" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H99" s="19" t="s">
+      <c r="H99" s="17" t="s">
         <v>6</v>
       </c>
       <c r="I99" s="1" t="e">
@@ -3351,36 +2725,36 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" ht="15" spans="1:9">
-      <c r="A100" s="10"/>
-      <c r="B100" s="11" t="s">
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" s="14"/>
+      <c r="B100" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D100" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
-      <c r="H100" s="19"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="17"/>
+      <c r="H100" s="17"/>
       <c r="I100" s="1" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="G101" s="18" t="str">
+      <c r="G101" s="7" t="str">
         <f t="shared" ref="G101:G132" si="8">IF(I101&gt;0,I101,IF(I101=0," ","ERROR"))</f>
-        <v> </v>
-      </c>
-      <c r="H101" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H101" s="1" t="e">
         <f>IF(AND(G101&lt;&gt;" ",G101&lt;&gt;"ERROR",H98&lt;&gt;" ",H98&lt;&gt;"ERROR"),G101+H98," ")</f>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I101" s="1">
         <f t="shared" si="7"/>
@@ -3388,13 +2762,13 @@
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="G102" s="18" t="str">
+      <c r="G102" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H102" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H102" s="1" t="e">
         <f t="shared" ref="H102:H132" si="9">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ",H101&lt;&gt;"ERROR"),G102+H101," ")</f>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I102" s="1">
         <f t="shared" si="7"/>
@@ -3402,13 +2776,13 @@
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="G103" s="18" t="str">
+      <c r="G103" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H103" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H103" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I103" s="1">
         <f t="shared" si="7"/>
@@ -3416,13 +2790,13 @@
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="G104" s="18" t="str">
+      <c r="G104" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H104" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H104" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I104" s="1">
         <f t="shared" si="7"/>
@@ -3430,13 +2804,13 @@
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="G105" s="18" t="str">
+      <c r="G105" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H105" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H105" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I105" s="1">
         <f t="shared" si="7"/>
@@ -3444,13 +2818,13 @@
       </c>
     </row>
     <row r="106" spans="1:9">
-      <c r="G106" s="18" t="str">
+      <c r="G106" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H106" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H106" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I106" s="1">
         <f t="shared" si="7"/>
@@ -3458,13 +2832,13 @@
       </c>
     </row>
     <row r="107" spans="1:9">
-      <c r="G107" s="18" t="str">
+      <c r="G107" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H107" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H107" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I107" s="1">
         <f t="shared" si="7"/>
@@ -3472,13 +2846,13 @@
       </c>
     </row>
     <row r="108" spans="1:9">
-      <c r="G108" s="18" t="str">
+      <c r="G108" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H108" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H108" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I108" s="1">
         <f t="shared" si="7"/>
@@ -3486,13 +2860,13 @@
       </c>
     </row>
     <row r="109" spans="1:9">
-      <c r="G109" s="18" t="str">
+      <c r="G109" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H109" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H109" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I109" s="1">
         <f t="shared" si="7"/>
@@ -3500,13 +2874,13 @@
       </c>
     </row>
     <row r="110" spans="1:9">
-      <c r="G110" s="18" t="str">
+      <c r="G110" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H110" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H110" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I110" s="1">
         <f t="shared" si="7"/>
@@ -3514,13 +2888,13 @@
       </c>
     </row>
     <row r="111" spans="1:9">
-      <c r="G111" s="18" t="str">
+      <c r="G111" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H111" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H111" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I111" s="1">
         <f t="shared" si="7"/>
@@ -3528,13 +2902,13 @@
       </c>
     </row>
     <row r="112" spans="1:9">
-      <c r="G112" s="18" t="str">
+      <c r="G112" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H112" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H112" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I112" s="1">
         <f t="shared" si="7"/>
@@ -3542,13 +2916,13 @@
       </c>
     </row>
     <row r="113" spans="7:9">
-      <c r="G113" s="18" t="str">
+      <c r="G113" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H113" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H113" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I113" s="1">
         <f t="shared" si="7"/>
@@ -3556,13 +2930,13 @@
       </c>
     </row>
     <row r="114" spans="7:9">
-      <c r="G114" s="18" t="str">
+      <c r="G114" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H114" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H114" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I114" s="1">
         <f t="shared" si="7"/>
@@ -3570,13 +2944,13 @@
       </c>
     </row>
     <row r="115" spans="7:9">
-      <c r="G115" s="18" t="str">
+      <c r="G115" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H115" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H115" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I115" s="1">
         <f t="shared" si="7"/>
@@ -3584,13 +2958,13 @@
       </c>
     </row>
     <row r="116" spans="7:9">
-      <c r="G116" s="18" t="str">
+      <c r="G116" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H116" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H116" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I116" s="1">
         <f t="shared" si="7"/>
@@ -3598,13 +2972,13 @@
       </c>
     </row>
     <row r="117" spans="7:9">
-      <c r="G117" s="18" t="str">
+      <c r="G117" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H117" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H117" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I117" s="1">
         <f t="shared" si="7"/>
@@ -3612,13 +2986,13 @@
       </c>
     </row>
     <row r="118" spans="7:9">
-      <c r="G118" s="18" t="str">
+      <c r="G118" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H118" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H118" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I118" s="1">
         <f t="shared" si="7"/>
@@ -3626,13 +3000,13 @@
       </c>
     </row>
     <row r="119" spans="7:9">
-      <c r="G119" s="18" t="str">
+      <c r="G119" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H119" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H119" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I119" s="1">
         <f t="shared" si="7"/>
@@ -3640,13 +3014,13 @@
       </c>
     </row>
     <row r="120" spans="7:9">
-      <c r="G120" s="18" t="str">
+      <c r="G120" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H120" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H120" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I120" s="1">
         <f t="shared" si="7"/>
@@ -3654,13 +3028,13 @@
       </c>
     </row>
     <row r="121" spans="7:9">
-      <c r="G121" s="18" t="str">
+      <c r="G121" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H121" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H121" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I121" s="1">
         <f t="shared" si="7"/>
@@ -3668,13 +3042,13 @@
       </c>
     </row>
     <row r="122" spans="7:9">
-      <c r="G122" s="18" t="str">
+      <c r="G122" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H122" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H122" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I122" s="1">
         <f t="shared" si="7"/>
@@ -3682,13 +3056,13 @@
       </c>
     </row>
     <row r="123" spans="7:9">
-      <c r="G123" s="18" t="str">
+      <c r="G123" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H123" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H123" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I123" s="1">
         <f t="shared" si="7"/>
@@ -3696,13 +3070,13 @@
       </c>
     </row>
     <row r="124" spans="7:9">
-      <c r="G124" s="18" t="str">
+      <c r="G124" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H124" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H124" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I124" s="1">
         <f t="shared" si="7"/>
@@ -3710,13 +3084,13 @@
       </c>
     </row>
     <row r="125" spans="7:9">
-      <c r="G125" s="18" t="str">
+      <c r="G125" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H125" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H125" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I125" s="1">
         <f t="shared" si="7"/>
@@ -3724,13 +3098,13 @@
       </c>
     </row>
     <row r="126" spans="7:9">
-      <c r="G126" s="18" t="str">
+      <c r="G126" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H126" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H126" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I126" s="1">
         <f t="shared" si="7"/>
@@ -3738,13 +3112,13 @@
       </c>
     </row>
     <row r="127" spans="7:9">
-      <c r="G127" s="18" t="str">
+      <c r="G127" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H127" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H127" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I127" s="1">
         <f t="shared" si="7"/>
@@ -3752,13 +3126,13 @@
       </c>
     </row>
     <row r="128" spans="7:9">
-      <c r="G128" s="18" t="str">
+      <c r="G128" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H128" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H128" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I128" s="1">
         <f t="shared" si="7"/>
@@ -3766,13 +3140,13 @@
       </c>
     </row>
     <row r="129" spans="7:9">
-      <c r="G129" s="18" t="str">
+      <c r="G129" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H129" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H129" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I129" s="1">
         <f t="shared" si="7"/>
@@ -3780,13 +3154,13 @@
       </c>
     </row>
     <row r="130" spans="7:9">
-      <c r="G130" s="18" t="str">
+      <c r="G130" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H130" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H130" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I130" s="1">
         <f t="shared" si="7"/>
@@ -3794,13 +3168,13 @@
       </c>
     </row>
     <row r="131" spans="7:9">
-      <c r="G131" s="18" t="str">
+      <c r="G131" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H131" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H131" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I131" s="1">
         <f t="shared" si="7"/>
@@ -3808,13 +3182,13 @@
       </c>
     </row>
     <row r="132" spans="7:9">
-      <c r="G132" s="18" t="str">
+      <c r="G132" s="7" t="str">
         <f t="shared" si="8"/>
-        <v> </v>
-      </c>
-      <c r="H132" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H132" s="1" t="e">
         <f t="shared" si="9"/>
-        <v> </v>
+        <v>#VALUE!</v>
       </c>
       <c r="I132" s="1">
         <f t="shared" si="7"/>
@@ -3823,11 +3197,14 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="G99:G100"/>
     <mergeCell ref="B65:C65"/>
     <mergeCell ref="D65:E65"/>
     <mergeCell ref="B99:C99"/>
@@ -3836,30 +3213,26 @@
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F31:F32"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="G99:G100"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H99:H100"/>
   </mergeCells>
-  <pageMargins left="0.748031496062992" right="0.748031496062992" top="0.984251968503937" bottom="0.984251968503937" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.74803149606299202" right="0.74803149606299202" top="0.98425196850393704" bottom="0.98425196850393704" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3868,10 +3241,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="12.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
